--- a/1. Comprehensive Plans/DATA GUIDE SF3.xlsx
+++ b/1. Comprehensive Plans/DATA GUIDE SF3.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jmccall\Documents\GIT\Regional Planning\Comprehensive Plans\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jmccall\Documents\GIT\Regional Planning\1. Comprehensive Plans\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F133EBC1-004B-429A-B1EA-9DB32E3F24E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECE035BB-6CDD-4F88-A429-00768B444624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22650" yWindow="4350" windowWidth="16710" windowHeight="7995" xr2:uid="{3D9E8CCC-2D26-47BF-8776-69666F0FF85F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{3D9E8CCC-2D26-47BF-8776-69666F0FF85F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2009" uniqueCount="1006">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1949" uniqueCount="989">
   <si>
     <t>Column Name</t>
   </si>
@@ -2369,57 +2369,6 @@
   </si>
   <si>
     <t>P082001</t>
-  </si>
-  <si>
-    <t>vehicles_tenurebyvehicles_total_series</t>
-  </si>
-  <si>
-    <t>vehicles_ownerocc_total</t>
-  </si>
-  <si>
-    <t>H044002</t>
-  </si>
-  <si>
-    <t>vehicles_ownerocc_novehicle</t>
-  </si>
-  <si>
-    <t>vehicles_ownerocc_1vehicle</t>
-  </si>
-  <si>
-    <t>vehicles_ownerocc_2vehicles</t>
-  </si>
-  <si>
-    <t>vehicles_ownerocc_3vehicles</t>
-  </si>
-  <si>
-    <t>vehicles_ownerocc_4vehicles</t>
-  </si>
-  <si>
-    <t>vehicles_ownerocc_5+vehicles</t>
-  </si>
-  <si>
-    <t>vehicles_renterocc_total</t>
-  </si>
-  <si>
-    <t>H044009</t>
-  </si>
-  <si>
-    <t>vehicles_renterocc_novehicle</t>
-  </si>
-  <si>
-    <t>vehicles_renterocc_1vehicle</t>
-  </si>
-  <si>
-    <t>vehicles_renterocc_2vehicles</t>
-  </si>
-  <si>
-    <t>vehicles_renterocc_3vehicles</t>
-  </si>
-  <si>
-    <t>vehicles_renterocc_4vehicles</t>
-  </si>
-  <si>
-    <t>vehicles_renterocc_5+vehicles</t>
   </si>
   <si>
     <t>industry_sexbyindustrycivilianpop_total_series</t>
@@ -3413,7 +3362,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C3BA02E-B3CC-4A06-80A3-2649C09AF45F}">
-  <dimension ref="A1:I501"/>
+  <dimension ref="A1:I486"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="67.28515625" bestFit="1" customWidth="1"/>
@@ -3428,7 +3377,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1005</v>
+        <v>988</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -4336,7 +4285,7 @@
         <v>14</v>
       </c>
       <c r="D32" t="s">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c r="E32" t="s">
         <v>74</v>
@@ -14512,13 +14461,13 @@
         <v>778</v>
       </c>
       <c r="C383" t="s">
-        <v>102</v>
+        <v>512</v>
       </c>
       <c r="D383" t="s">
-        <v>136</v>
+        <v>779</v>
       </c>
       <c r="E383" t="s">
-        <v>137</v>
+        <v>780</v>
       </c>
       <c r="F383">
         <v>1</v>
@@ -14530,7 +14479,7 @@
         <v>0</v>
       </c>
       <c r="I383">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="384" spans="1:9" x14ac:dyDescent="0.25">
@@ -14538,16 +14487,16 @@
         <v>383</v>
       </c>
       <c r="B384" t="s">
+        <v>781</v>
+      </c>
+      <c r="C384" t="s">
+        <v>512</v>
+      </c>
+      <c r="D384" t="s">
         <v>779</v>
       </c>
-      <c r="C384" t="s">
-        <v>102</v>
-      </c>
-      <c r="D384" t="s">
-        <v>136</v>
-      </c>
       <c r="E384" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="F384">
         <v>1</v>
@@ -14559,7 +14508,7 @@
         <v>0</v>
       </c>
       <c r="I384">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="385" spans="1:9" x14ac:dyDescent="0.25">
@@ -14567,16 +14516,16 @@
         <v>384</v>
       </c>
       <c r="B385" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="C385" t="s">
-        <v>102</v>
+        <v>512</v>
       </c>
       <c r="D385" t="s">
-        <v>136</v>
+        <v>779</v>
       </c>
       <c r="E385" t="s">
-        <v>139</v>
+        <v>784</v>
       </c>
       <c r="F385">
         <v>1</v>
@@ -14588,7 +14537,7 @@
         <v>0</v>
       </c>
       <c r="I385">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="386" spans="1:9" x14ac:dyDescent="0.25">
@@ -14596,16 +14545,16 @@
         <v>385</v>
       </c>
       <c r="B386" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="C386" t="s">
-        <v>102</v>
+        <v>512</v>
       </c>
       <c r="D386" t="s">
-        <v>136</v>
+        <v>779</v>
       </c>
       <c r="E386" t="s">
-        <v>141</v>
+        <v>786</v>
       </c>
       <c r="F386">
         <v>1</v>
@@ -14617,7 +14566,7 @@
         <v>0</v>
       </c>
       <c r="I386">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="387" spans="1:9" x14ac:dyDescent="0.25">
@@ -14625,16 +14574,16 @@
         <v>386</v>
       </c>
       <c r="B387" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="C387" t="s">
-        <v>102</v>
+        <v>512</v>
       </c>
       <c r="D387" t="s">
-        <v>136</v>
+        <v>779</v>
       </c>
       <c r="E387" t="s">
-        <v>143</v>
+        <v>788</v>
       </c>
       <c r="F387">
         <v>1</v>
@@ -14646,7 +14595,7 @@
         <v>0</v>
       </c>
       <c r="I387">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="388" spans="1:9" x14ac:dyDescent="0.25">
@@ -14654,16 +14603,16 @@
         <v>387</v>
       </c>
       <c r="B388" t="s">
-        <v>784</v>
+        <v>789</v>
       </c>
       <c r="C388" t="s">
-        <v>102</v>
+        <v>512</v>
       </c>
       <c r="D388" t="s">
-        <v>136</v>
+        <v>779</v>
       </c>
       <c r="E388" t="s">
-        <v>145</v>
+        <v>790</v>
       </c>
       <c r="F388">
         <v>1</v>
@@ -14675,7 +14624,7 @@
         <v>0</v>
       </c>
       <c r="I388">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="389" spans="1:9" x14ac:dyDescent="0.25">
@@ -14683,16 +14632,16 @@
         <v>388</v>
       </c>
       <c r="B389" t="s">
-        <v>785</v>
+        <v>791</v>
       </c>
       <c r="C389" t="s">
-        <v>102</v>
+        <v>512</v>
       </c>
       <c r="D389" t="s">
-        <v>136</v>
+        <v>779</v>
       </c>
       <c r="E389" t="s">
-        <v>147</v>
+        <v>792</v>
       </c>
       <c r="F389">
         <v>1</v>
@@ -14704,7 +14653,7 @@
         <v>0</v>
       </c>
       <c r="I389">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="390" spans="1:9" x14ac:dyDescent="0.25">
@@ -14712,16 +14661,16 @@
         <v>389</v>
       </c>
       <c r="B390" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="C390" t="s">
-        <v>102</v>
+        <v>512</v>
       </c>
       <c r="D390" t="s">
-        <v>136</v>
+        <v>779</v>
       </c>
       <c r="E390" t="s">
-        <v>149</v>
+        <v>794</v>
       </c>
       <c r="F390">
         <v>1</v>
@@ -14733,7 +14682,7 @@
         <v>0</v>
       </c>
       <c r="I390">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="391" spans="1:9" x14ac:dyDescent="0.25">
@@ -14741,16 +14690,16 @@
         <v>390</v>
       </c>
       <c r="B391" t="s">
-        <v>787</v>
+        <v>795</v>
       </c>
       <c r="C391" t="s">
-        <v>102</v>
+        <v>512</v>
       </c>
       <c r="D391" t="s">
-        <v>136</v>
+        <v>779</v>
       </c>
       <c r="E391" t="s">
-        <v>788</v>
+        <v>796</v>
       </c>
       <c r="F391">
         <v>1</v>
@@ -14762,7 +14711,7 @@
         <v>0</v>
       </c>
       <c r="I391">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="392" spans="1:9" x14ac:dyDescent="0.25">
@@ -14770,16 +14719,16 @@
         <v>391</v>
       </c>
       <c r="B392" t="s">
-        <v>789</v>
+        <v>797</v>
       </c>
       <c r="C392" t="s">
-        <v>102</v>
+        <v>512</v>
       </c>
       <c r="D392" t="s">
-        <v>136</v>
+        <v>779</v>
       </c>
       <c r="E392" t="s">
-        <v>151</v>
+        <v>798</v>
       </c>
       <c r="F392">
         <v>1</v>
@@ -14791,7 +14740,7 @@
         <v>0</v>
       </c>
       <c r="I392">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="393" spans="1:9" x14ac:dyDescent="0.25">
@@ -14799,16 +14748,16 @@
         <v>392</v>
       </c>
       <c r="B393" t="s">
-        <v>790</v>
+        <v>799</v>
       </c>
       <c r="C393" t="s">
-        <v>102</v>
+        <v>512</v>
       </c>
       <c r="D393" t="s">
-        <v>136</v>
+        <v>779</v>
       </c>
       <c r="E393" t="s">
-        <v>153</v>
+        <v>800</v>
       </c>
       <c r="F393">
         <v>1</v>
@@ -14820,7 +14769,7 @@
         <v>0</v>
       </c>
       <c r="I393">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="394" spans="1:9" x14ac:dyDescent="0.25">
@@ -14828,16 +14777,16 @@
         <v>393</v>
       </c>
       <c r="B394" t="s">
-        <v>791</v>
+        <v>801</v>
       </c>
       <c r="C394" t="s">
-        <v>102</v>
+        <v>512</v>
       </c>
       <c r="D394" t="s">
-        <v>136</v>
+        <v>779</v>
       </c>
       <c r="E394" t="s">
-        <v>155</v>
+        <v>802</v>
       </c>
       <c r="F394">
         <v>1</v>
@@ -14849,7 +14798,7 @@
         <v>0</v>
       </c>
       <c r="I394">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="395" spans="1:9" x14ac:dyDescent="0.25">
@@ -14857,16 +14806,16 @@
         <v>394</v>
       </c>
       <c r="B395" t="s">
-        <v>792</v>
+        <v>803</v>
       </c>
       <c r="C395" t="s">
-        <v>102</v>
+        <v>512</v>
       </c>
       <c r="D395" t="s">
-        <v>136</v>
+        <v>779</v>
       </c>
       <c r="E395" t="s">
-        <v>157</v>
+        <v>804</v>
       </c>
       <c r="F395">
         <v>1</v>
@@ -14878,7 +14827,7 @@
         <v>0</v>
       </c>
       <c r="I395">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="396" spans="1:9" x14ac:dyDescent="0.25">
@@ -14886,16 +14835,16 @@
         <v>395</v>
       </c>
       <c r="B396" t="s">
-        <v>793</v>
+        <v>805</v>
       </c>
       <c r="C396" t="s">
-        <v>102</v>
+        <v>512</v>
       </c>
       <c r="D396" t="s">
-        <v>136</v>
+        <v>779</v>
       </c>
       <c r="E396" t="s">
-        <v>159</v>
+        <v>806</v>
       </c>
       <c r="F396">
         <v>1</v>
@@ -14907,7 +14856,7 @@
         <v>0</v>
       </c>
       <c r="I396">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="397" spans="1:9" x14ac:dyDescent="0.25">
@@ -14915,16 +14864,16 @@
         <v>396</v>
       </c>
       <c r="B397" t="s">
-        <v>794</v>
+        <v>807</v>
       </c>
       <c r="C397" t="s">
-        <v>102</v>
+        <v>512</v>
       </c>
       <c r="D397" t="s">
-        <v>136</v>
+        <v>779</v>
       </c>
       <c r="E397" t="s">
-        <v>161</v>
+        <v>808</v>
       </c>
       <c r="F397">
         <v>1</v>
@@ -14936,7 +14885,7 @@
         <v>0</v>
       </c>
       <c r="I397">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="398" spans="1:9" x14ac:dyDescent="0.25">
@@ -14944,16 +14893,16 @@
         <v>397</v>
       </c>
       <c r="B398" t="s">
-        <v>795</v>
+        <v>809</v>
       </c>
       <c r="C398" t="s">
         <v>512</v>
       </c>
       <c r="D398" t="s">
-        <v>796</v>
+        <v>779</v>
       </c>
       <c r="E398" t="s">
-        <v>797</v>
+        <v>810</v>
       </c>
       <c r="F398">
         <v>1</v>
@@ -14973,16 +14922,16 @@
         <v>398</v>
       </c>
       <c r="B399" t="s">
-        <v>798</v>
+        <v>811</v>
       </c>
       <c r="C399" t="s">
         <v>512</v>
       </c>
       <c r="D399" t="s">
-        <v>796</v>
+        <v>779</v>
       </c>
       <c r="E399" t="s">
-        <v>799</v>
+        <v>812</v>
       </c>
       <c r="F399">
         <v>1</v>
@@ -15002,16 +14951,16 @@
         <v>399</v>
       </c>
       <c r="B400" t="s">
-        <v>800</v>
+        <v>813</v>
       </c>
       <c r="C400" t="s">
         <v>512</v>
       </c>
       <c r="D400" t="s">
-        <v>796</v>
+        <v>779</v>
       </c>
       <c r="E400" t="s">
-        <v>801</v>
+        <v>814</v>
       </c>
       <c r="F400">
         <v>1</v>
@@ -15031,16 +14980,16 @@
         <v>400</v>
       </c>
       <c r="B401" t="s">
-        <v>802</v>
+        <v>815</v>
       </c>
       <c r="C401" t="s">
         <v>512</v>
       </c>
       <c r="D401" t="s">
-        <v>796</v>
+        <v>779</v>
       </c>
       <c r="E401" t="s">
-        <v>803</v>
+        <v>816</v>
       </c>
       <c r="F401">
         <v>1</v>
@@ -15060,16 +15009,16 @@
         <v>401</v>
       </c>
       <c r="B402" t="s">
-        <v>804</v>
+        <v>817</v>
       </c>
       <c r="C402" t="s">
         <v>512</v>
       </c>
       <c r="D402" t="s">
-        <v>796</v>
+        <v>779</v>
       </c>
       <c r="E402" t="s">
-        <v>805</v>
+        <v>818</v>
       </c>
       <c r="F402">
         <v>1</v>
@@ -15089,16 +15038,16 @@
         <v>402</v>
       </c>
       <c r="B403" t="s">
-        <v>806</v>
+        <v>819</v>
       </c>
       <c r="C403" t="s">
         <v>512</v>
       </c>
       <c r="D403" t="s">
-        <v>796</v>
+        <v>779</v>
       </c>
       <c r="E403" t="s">
-        <v>807</v>
+        <v>820</v>
       </c>
       <c r="F403">
         <v>1</v>
@@ -15118,16 +15067,16 @@
         <v>403</v>
       </c>
       <c r="B404" t="s">
-        <v>808</v>
+        <v>821</v>
       </c>
       <c r="C404" t="s">
         <v>512</v>
       </c>
       <c r="D404" t="s">
-        <v>796</v>
+        <v>779</v>
       </c>
       <c r="E404" t="s">
-        <v>809</v>
+        <v>822</v>
       </c>
       <c r="F404">
         <v>1</v>
@@ -15147,16 +15096,16 @@
         <v>404</v>
       </c>
       <c r="B405" t="s">
-        <v>810</v>
+        <v>823</v>
       </c>
       <c r="C405" t="s">
         <v>512</v>
       </c>
       <c r="D405" t="s">
-        <v>796</v>
+        <v>779</v>
       </c>
       <c r="E405" t="s">
-        <v>811</v>
+        <v>824</v>
       </c>
       <c r="F405">
         <v>1</v>
@@ -15176,16 +15125,16 @@
         <v>405</v>
       </c>
       <c r="B406" t="s">
-        <v>812</v>
+        <v>825</v>
       </c>
       <c r="C406" t="s">
         <v>512</v>
       </c>
       <c r="D406" t="s">
-        <v>796</v>
+        <v>779</v>
       </c>
       <c r="E406" t="s">
-        <v>813</v>
+        <v>826</v>
       </c>
       <c r="F406">
         <v>1</v>
@@ -15205,16 +15154,16 @@
         <v>406</v>
       </c>
       <c r="B407" t="s">
-        <v>814</v>
+        <v>827</v>
       </c>
       <c r="C407" t="s">
         <v>512</v>
       </c>
       <c r="D407" t="s">
-        <v>796</v>
+        <v>779</v>
       </c>
       <c r="E407" t="s">
-        <v>815</v>
+        <v>828</v>
       </c>
       <c r="F407">
         <v>1</v>
@@ -15234,16 +15183,16 @@
         <v>407</v>
       </c>
       <c r="B408" t="s">
-        <v>816</v>
+        <v>829</v>
       </c>
       <c r="C408" t="s">
         <v>512</v>
       </c>
       <c r="D408" t="s">
-        <v>796</v>
+        <v>779</v>
       </c>
       <c r="E408" t="s">
-        <v>817</v>
+        <v>830</v>
       </c>
       <c r="F408">
         <v>1</v>
@@ -15263,16 +15212,16 @@
         <v>408</v>
       </c>
       <c r="B409" t="s">
-        <v>818</v>
+        <v>831</v>
       </c>
       <c r="C409" t="s">
         <v>512</v>
       </c>
       <c r="D409" t="s">
-        <v>796</v>
+        <v>779</v>
       </c>
       <c r="E409" t="s">
-        <v>819</v>
+        <v>832</v>
       </c>
       <c r="F409">
         <v>1</v>
@@ -15292,16 +15241,16 @@
         <v>409</v>
       </c>
       <c r="B410" t="s">
-        <v>820</v>
+        <v>833</v>
       </c>
       <c r="C410" t="s">
         <v>512</v>
       </c>
       <c r="D410" t="s">
-        <v>796</v>
+        <v>779</v>
       </c>
       <c r="E410" t="s">
-        <v>821</v>
+        <v>834</v>
       </c>
       <c r="F410">
         <v>1</v>
@@ -15321,16 +15270,16 @@
         <v>410</v>
       </c>
       <c r="B411" t="s">
-        <v>822</v>
+        <v>835</v>
       </c>
       <c r="C411" t="s">
         <v>512</v>
       </c>
       <c r="D411" t="s">
-        <v>796</v>
+        <v>779</v>
       </c>
       <c r="E411" t="s">
-        <v>823</v>
+        <v>836</v>
       </c>
       <c r="F411">
         <v>1</v>
@@ -15350,16 +15299,16 @@
         <v>411</v>
       </c>
       <c r="B412" t="s">
-        <v>824</v>
+        <v>837</v>
       </c>
       <c r="C412" t="s">
         <v>512</v>
       </c>
       <c r="D412" t="s">
-        <v>796</v>
+        <v>779</v>
       </c>
       <c r="E412" t="s">
-        <v>825</v>
+        <v>838</v>
       </c>
       <c r="F412">
         <v>1</v>
@@ -15379,16 +15328,16 @@
         <v>412</v>
       </c>
       <c r="B413" t="s">
-        <v>826</v>
+        <v>839</v>
       </c>
       <c r="C413" t="s">
         <v>512</v>
       </c>
       <c r="D413" t="s">
-        <v>796</v>
+        <v>779</v>
       </c>
       <c r="E413" t="s">
-        <v>827</v>
+        <v>840</v>
       </c>
       <c r="F413">
         <v>1</v>
@@ -15408,16 +15357,16 @@
         <v>413</v>
       </c>
       <c r="B414" t="s">
-        <v>828</v>
+        <v>841</v>
       </c>
       <c r="C414" t="s">
         <v>512</v>
       </c>
       <c r="D414" t="s">
-        <v>796</v>
+        <v>779</v>
       </c>
       <c r="E414" t="s">
-        <v>829</v>
+        <v>842</v>
       </c>
       <c r="F414">
         <v>1</v>
@@ -15437,16 +15386,16 @@
         <v>414</v>
       </c>
       <c r="B415" t="s">
-        <v>830</v>
+        <v>843</v>
       </c>
       <c r="C415" t="s">
         <v>512</v>
       </c>
       <c r="D415" t="s">
-        <v>796</v>
+        <v>779</v>
       </c>
       <c r="E415" t="s">
-        <v>831</v>
+        <v>844</v>
       </c>
       <c r="F415">
         <v>1</v>
@@ -15466,16 +15415,16 @@
         <v>415</v>
       </c>
       <c r="B416" t="s">
-        <v>832</v>
+        <v>845</v>
       </c>
       <c r="C416" t="s">
         <v>512</v>
       </c>
       <c r="D416" t="s">
-        <v>796</v>
+        <v>779</v>
       </c>
       <c r="E416" t="s">
-        <v>833</v>
+        <v>846</v>
       </c>
       <c r="F416">
         <v>1</v>
@@ -15495,16 +15444,16 @@
         <v>416</v>
       </c>
       <c r="B417" t="s">
-        <v>834</v>
+        <v>847</v>
       </c>
       <c r="C417" t="s">
         <v>512</v>
       </c>
       <c r="D417" t="s">
-        <v>796</v>
+        <v>779</v>
       </c>
       <c r="E417" t="s">
-        <v>835</v>
+        <v>848</v>
       </c>
       <c r="F417">
         <v>1</v>
@@ -15524,16 +15473,16 @@
         <v>417</v>
       </c>
       <c r="B418" t="s">
-        <v>836</v>
+        <v>849</v>
       </c>
       <c r="C418" t="s">
         <v>512</v>
       </c>
       <c r="D418" t="s">
-        <v>796</v>
+        <v>779</v>
       </c>
       <c r="E418" t="s">
-        <v>837</v>
+        <v>850</v>
       </c>
       <c r="F418">
         <v>1</v>
@@ -15553,16 +15502,16 @@
         <v>418</v>
       </c>
       <c r="B419" t="s">
-        <v>838</v>
+        <v>851</v>
       </c>
       <c r="C419" t="s">
         <v>512</v>
       </c>
       <c r="D419" t="s">
-        <v>796</v>
+        <v>779</v>
       </c>
       <c r="E419" t="s">
-        <v>839</v>
+        <v>852</v>
       </c>
       <c r="F419">
         <v>1</v>
@@ -15582,16 +15531,16 @@
         <v>419</v>
       </c>
       <c r="B420" t="s">
-        <v>840</v>
+        <v>853</v>
       </c>
       <c r="C420" t="s">
         <v>512</v>
       </c>
       <c r="D420" t="s">
-        <v>796</v>
+        <v>779</v>
       </c>
       <c r="E420" t="s">
-        <v>841</v>
+        <v>854</v>
       </c>
       <c r="F420">
         <v>1</v>
@@ -15611,16 +15560,16 @@
         <v>420</v>
       </c>
       <c r="B421" t="s">
-        <v>842</v>
+        <v>855</v>
       </c>
       <c r="C421" t="s">
         <v>512</v>
       </c>
       <c r="D421" t="s">
-        <v>796</v>
+        <v>779</v>
       </c>
       <c r="E421" t="s">
-        <v>843</v>
+        <v>856</v>
       </c>
       <c r="F421">
         <v>1</v>
@@ -15640,16 +15589,16 @@
         <v>421</v>
       </c>
       <c r="B422" t="s">
-        <v>844</v>
+        <v>857</v>
       </c>
       <c r="C422" t="s">
         <v>512</v>
       </c>
       <c r="D422" t="s">
-        <v>796</v>
+        <v>779</v>
       </c>
       <c r="E422" t="s">
-        <v>845</v>
+        <v>858</v>
       </c>
       <c r="F422">
         <v>1</v>
@@ -15669,16 +15618,16 @@
         <v>422</v>
       </c>
       <c r="B423" t="s">
-        <v>846</v>
+        <v>859</v>
       </c>
       <c r="C423" t="s">
         <v>512</v>
       </c>
       <c r="D423" t="s">
-        <v>796</v>
+        <v>779</v>
       </c>
       <c r="E423" t="s">
-        <v>847</v>
+        <v>860</v>
       </c>
       <c r="F423">
         <v>1</v>
@@ -15698,16 +15647,16 @@
         <v>423</v>
       </c>
       <c r="B424" t="s">
-        <v>848</v>
+        <v>861</v>
       </c>
       <c r="C424" t="s">
         <v>512</v>
       </c>
       <c r="D424" t="s">
-        <v>796</v>
+        <v>779</v>
       </c>
       <c r="E424" t="s">
-        <v>849</v>
+        <v>862</v>
       </c>
       <c r="F424">
         <v>1</v>
@@ -15727,16 +15676,16 @@
         <v>424</v>
       </c>
       <c r="B425" t="s">
-        <v>850</v>
+        <v>863</v>
       </c>
       <c r="C425" t="s">
         <v>512</v>
       </c>
       <c r="D425" t="s">
-        <v>796</v>
+        <v>779</v>
       </c>
       <c r="E425" t="s">
-        <v>851</v>
+        <v>864</v>
       </c>
       <c r="F425">
         <v>1</v>
@@ -15756,16 +15705,16 @@
         <v>425</v>
       </c>
       <c r="B426" t="s">
-        <v>852</v>
+        <v>865</v>
       </c>
       <c r="C426" t="s">
         <v>512</v>
       </c>
       <c r="D426" t="s">
-        <v>796</v>
+        <v>779</v>
       </c>
       <c r="E426" t="s">
-        <v>853</v>
+        <v>866</v>
       </c>
       <c r="F426">
         <v>1</v>
@@ -15785,16 +15734,16 @@
         <v>426</v>
       </c>
       <c r="B427" t="s">
-        <v>854</v>
+        <v>867</v>
       </c>
       <c r="C427" t="s">
         <v>512</v>
       </c>
       <c r="D427" t="s">
-        <v>796</v>
+        <v>779</v>
       </c>
       <c r="E427" t="s">
-        <v>855</v>
+        <v>868</v>
       </c>
       <c r="F427">
         <v>1</v>
@@ -15814,16 +15763,16 @@
         <v>427</v>
       </c>
       <c r="B428" t="s">
-        <v>856</v>
+        <v>869</v>
       </c>
       <c r="C428" t="s">
         <v>512</v>
       </c>
       <c r="D428" t="s">
-        <v>796</v>
+        <v>779</v>
       </c>
       <c r="E428" t="s">
-        <v>857</v>
+        <v>870</v>
       </c>
       <c r="F428">
         <v>1</v>
@@ -15843,16 +15792,16 @@
         <v>428</v>
       </c>
       <c r="B429" t="s">
-        <v>858</v>
+        <v>871</v>
       </c>
       <c r="C429" t="s">
         <v>512</v>
       </c>
       <c r="D429" t="s">
-        <v>796</v>
+        <v>779</v>
       </c>
       <c r="E429" t="s">
-        <v>859</v>
+        <v>872</v>
       </c>
       <c r="F429">
         <v>1</v>
@@ -15872,16 +15821,16 @@
         <v>429</v>
       </c>
       <c r="B430" t="s">
-        <v>860</v>
+        <v>873</v>
       </c>
       <c r="C430" t="s">
         <v>512</v>
       </c>
       <c r="D430" t="s">
-        <v>796</v>
+        <v>779</v>
       </c>
       <c r="E430" t="s">
-        <v>861</v>
+        <v>874</v>
       </c>
       <c r="F430">
         <v>1</v>
@@ -15901,16 +15850,16 @@
         <v>430</v>
       </c>
       <c r="B431" t="s">
-        <v>862</v>
+        <v>875</v>
       </c>
       <c r="C431" t="s">
         <v>512</v>
       </c>
       <c r="D431" t="s">
-        <v>796</v>
+        <v>779</v>
       </c>
       <c r="E431" t="s">
-        <v>863</v>
+        <v>876</v>
       </c>
       <c r="F431">
         <v>1</v>
@@ -15930,16 +15879,16 @@
         <v>431</v>
       </c>
       <c r="B432" t="s">
-        <v>864</v>
+        <v>877</v>
       </c>
       <c r="C432" t="s">
         <v>512</v>
       </c>
       <c r="D432" t="s">
-        <v>796</v>
+        <v>779</v>
       </c>
       <c r="E432" t="s">
-        <v>865</v>
+        <v>878</v>
       </c>
       <c r="F432">
         <v>1</v>
@@ -15959,16 +15908,16 @@
         <v>432</v>
       </c>
       <c r="B433" t="s">
-        <v>866</v>
+        <v>879</v>
       </c>
       <c r="C433" t="s">
         <v>512</v>
       </c>
       <c r="D433" t="s">
-        <v>796</v>
+        <v>779</v>
       </c>
       <c r="E433" t="s">
-        <v>867</v>
+        <v>880</v>
       </c>
       <c r="F433">
         <v>1</v>
@@ -15988,16 +15937,16 @@
         <v>433</v>
       </c>
       <c r="B434" t="s">
-        <v>868</v>
+        <v>881</v>
       </c>
       <c r="C434" t="s">
         <v>512</v>
       </c>
       <c r="D434" t="s">
-        <v>796</v>
+        <v>779</v>
       </c>
       <c r="E434" t="s">
-        <v>869</v>
+        <v>882</v>
       </c>
       <c r="F434">
         <v>1</v>
@@ -16017,16 +15966,16 @@
         <v>434</v>
       </c>
       <c r="B435" t="s">
-        <v>870</v>
+        <v>883</v>
       </c>
       <c r="C435" t="s">
         <v>512</v>
       </c>
       <c r="D435" t="s">
-        <v>796</v>
+        <v>779</v>
       </c>
       <c r="E435" t="s">
-        <v>871</v>
+        <v>884</v>
       </c>
       <c r="F435">
         <v>1</v>
@@ -16046,16 +15995,16 @@
         <v>435</v>
       </c>
       <c r="B436" t="s">
-        <v>872</v>
+        <v>885</v>
       </c>
       <c r="C436" t="s">
         <v>512</v>
       </c>
       <c r="D436" t="s">
-        <v>796</v>
+        <v>779</v>
       </c>
       <c r="E436" t="s">
-        <v>873</v>
+        <v>886</v>
       </c>
       <c r="F436">
         <v>1</v>
@@ -16075,16 +16024,16 @@
         <v>436</v>
       </c>
       <c r="B437" t="s">
-        <v>874</v>
+        <v>887</v>
       </c>
       <c r="C437" t="s">
         <v>512</v>
       </c>
       <c r="D437" t="s">
-        <v>796</v>
+        <v>779</v>
       </c>
       <c r="E437" t="s">
-        <v>875</v>
+        <v>888</v>
       </c>
       <c r="F437">
         <v>1</v>
@@ -16104,16 +16053,16 @@
         <v>437</v>
       </c>
       <c r="B438" t="s">
-        <v>876</v>
+        <v>889</v>
       </c>
       <c r="C438" t="s">
         <v>512</v>
       </c>
       <c r="D438" t="s">
-        <v>796</v>
+        <v>987</v>
       </c>
       <c r="E438" t="s">
-        <v>877</v>
+        <v>890</v>
       </c>
       <c r="F438">
         <v>1</v>
@@ -16125,7 +16074,7 @@
         <v>0</v>
       </c>
       <c r="I438">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="439" spans="1:9" x14ac:dyDescent="0.25">
@@ -16133,16 +16082,16 @@
         <v>438</v>
       </c>
       <c r="B439" t="s">
-        <v>878</v>
+        <v>891</v>
       </c>
       <c r="C439" t="s">
         <v>512</v>
       </c>
       <c r="D439" t="s">
-        <v>796</v>
+        <v>987</v>
       </c>
       <c r="E439" t="s">
-        <v>879</v>
+        <v>892</v>
       </c>
       <c r="F439">
         <v>1</v>
@@ -16154,7 +16103,7 @@
         <v>0</v>
       </c>
       <c r="I439">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="440" spans="1:9" x14ac:dyDescent="0.25">
@@ -16162,16 +16111,16 @@
         <v>439</v>
       </c>
       <c r="B440" t="s">
-        <v>880</v>
+        <v>893</v>
       </c>
       <c r="C440" t="s">
         <v>512</v>
       </c>
       <c r="D440" t="s">
-        <v>796</v>
+        <v>987</v>
       </c>
       <c r="E440" t="s">
-        <v>881</v>
+        <v>894</v>
       </c>
       <c r="F440">
         <v>1</v>
@@ -16183,7 +16132,7 @@
         <v>0</v>
       </c>
       <c r="I440">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="441" spans="1:9" x14ac:dyDescent="0.25">
@@ -16191,16 +16140,16 @@
         <v>440</v>
       </c>
       <c r="B441" t="s">
-        <v>882</v>
+        <v>895</v>
       </c>
       <c r="C441" t="s">
         <v>512</v>
       </c>
       <c r="D441" t="s">
-        <v>796</v>
+        <v>987</v>
       </c>
       <c r="E441" t="s">
-        <v>883</v>
+        <v>896</v>
       </c>
       <c r="F441">
         <v>1</v>
@@ -16212,7 +16161,7 @@
         <v>0</v>
       </c>
       <c r="I441">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="442" spans="1:9" x14ac:dyDescent="0.25">
@@ -16220,16 +16169,16 @@
         <v>441</v>
       </c>
       <c r="B442" t="s">
-        <v>884</v>
+        <v>897</v>
       </c>
       <c r="C442" t="s">
         <v>512</v>
       </c>
       <c r="D442" t="s">
-        <v>796</v>
+        <v>987</v>
       </c>
       <c r="E442" t="s">
-        <v>885</v>
+        <v>898</v>
       </c>
       <c r="F442">
         <v>1</v>
@@ -16241,7 +16190,7 @@
         <v>0</v>
       </c>
       <c r="I442">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="443" spans="1:9" x14ac:dyDescent="0.25">
@@ -16249,16 +16198,16 @@
         <v>442</v>
       </c>
       <c r="B443" t="s">
-        <v>886</v>
+        <v>899</v>
       </c>
       <c r="C443" t="s">
         <v>512</v>
       </c>
       <c r="D443" t="s">
-        <v>796</v>
+        <v>987</v>
       </c>
       <c r="E443" t="s">
-        <v>887</v>
+        <v>900</v>
       </c>
       <c r="F443">
         <v>1</v>
@@ -16270,7 +16219,7 @@
         <v>0</v>
       </c>
       <c r="I443">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="444" spans="1:9" x14ac:dyDescent="0.25">
@@ -16278,16 +16227,16 @@
         <v>443</v>
       </c>
       <c r="B444" t="s">
-        <v>888</v>
+        <v>901</v>
       </c>
       <c r="C444" t="s">
         <v>512</v>
       </c>
       <c r="D444" t="s">
-        <v>796</v>
+        <v>987</v>
       </c>
       <c r="E444" t="s">
-        <v>889</v>
+        <v>902</v>
       </c>
       <c r="F444">
         <v>1</v>
@@ -16299,7 +16248,7 @@
         <v>0</v>
       </c>
       <c r="I444">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="445" spans="1:9" x14ac:dyDescent="0.25">
@@ -16307,16 +16256,16 @@
         <v>444</v>
       </c>
       <c r="B445" t="s">
-        <v>890</v>
+        <v>903</v>
       </c>
       <c r="C445" t="s">
         <v>512</v>
       </c>
       <c r="D445" t="s">
-        <v>796</v>
+        <v>987</v>
       </c>
       <c r="E445" t="s">
-        <v>891</v>
+        <v>904</v>
       </c>
       <c r="F445">
         <v>1</v>
@@ -16328,7 +16277,7 @@
         <v>0</v>
       </c>
       <c r="I445">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="446" spans="1:9" x14ac:dyDescent="0.25">
@@ -16336,16 +16285,16 @@
         <v>445</v>
       </c>
       <c r="B446" t="s">
-        <v>892</v>
+        <v>905</v>
       </c>
       <c r="C446" t="s">
         <v>512</v>
       </c>
       <c r="D446" t="s">
-        <v>796</v>
+        <v>987</v>
       </c>
       <c r="E446" t="s">
-        <v>893</v>
+        <v>906</v>
       </c>
       <c r="F446">
         <v>1</v>
@@ -16357,7 +16306,7 @@
         <v>0</v>
       </c>
       <c r="I446">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="447" spans="1:9" x14ac:dyDescent="0.25">
@@ -16365,16 +16314,16 @@
         <v>446</v>
       </c>
       <c r="B447" t="s">
-        <v>894</v>
+        <v>907</v>
       </c>
       <c r="C447" t="s">
         <v>512</v>
       </c>
       <c r="D447" t="s">
-        <v>796</v>
+        <v>987</v>
       </c>
       <c r="E447" t="s">
-        <v>895</v>
+        <v>908</v>
       </c>
       <c r="F447">
         <v>1</v>
@@ -16386,7 +16335,7 @@
         <v>0</v>
       </c>
       <c r="I447">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="448" spans="1:9" x14ac:dyDescent="0.25">
@@ -16394,16 +16343,16 @@
         <v>447</v>
       </c>
       <c r="B448" t="s">
-        <v>896</v>
+        <v>909</v>
       </c>
       <c r="C448" t="s">
         <v>512</v>
       </c>
       <c r="D448" t="s">
-        <v>796</v>
+        <v>987</v>
       </c>
       <c r="E448" t="s">
-        <v>897</v>
+        <v>910</v>
       </c>
       <c r="F448">
         <v>1</v>
@@ -16415,7 +16364,7 @@
         <v>0</v>
       </c>
       <c r="I448">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="449" spans="1:9" x14ac:dyDescent="0.25">
@@ -16423,16 +16372,16 @@
         <v>448</v>
       </c>
       <c r="B449" t="s">
-        <v>898</v>
+        <v>911</v>
       </c>
       <c r="C449" t="s">
         <v>512</v>
       </c>
       <c r="D449" t="s">
-        <v>796</v>
+        <v>987</v>
       </c>
       <c r="E449" t="s">
-        <v>899</v>
+        <v>912</v>
       </c>
       <c r="F449">
         <v>1</v>
@@ -16444,7 +16393,7 @@
         <v>0</v>
       </c>
       <c r="I449">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="450" spans="1:9" x14ac:dyDescent="0.25">
@@ -16452,16 +16401,16 @@
         <v>449</v>
       </c>
       <c r="B450" t="s">
-        <v>900</v>
+        <v>913</v>
       </c>
       <c r="C450" t="s">
         <v>512</v>
       </c>
       <c r="D450" t="s">
-        <v>796</v>
+        <v>987</v>
       </c>
       <c r="E450" t="s">
-        <v>901</v>
+        <v>914</v>
       </c>
       <c r="F450">
         <v>1</v>
@@ -16473,7 +16422,7 @@
         <v>0</v>
       </c>
       <c r="I450">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="451" spans="1:9" x14ac:dyDescent="0.25">
@@ -16481,16 +16430,16 @@
         <v>450</v>
       </c>
       <c r="B451" t="s">
-        <v>902</v>
+        <v>915</v>
       </c>
       <c r="C451" t="s">
         <v>512</v>
       </c>
       <c r="D451" t="s">
-        <v>796</v>
+        <v>987</v>
       </c>
       <c r="E451" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
       <c r="F451">
         <v>1</v>
@@ -16502,7 +16451,7 @@
         <v>0</v>
       </c>
       <c r="I451">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="452" spans="1:9" x14ac:dyDescent="0.25">
@@ -16510,16 +16459,16 @@
         <v>451</v>
       </c>
       <c r="B452" t="s">
-        <v>904</v>
+        <v>917</v>
       </c>
       <c r="C452" t="s">
         <v>512</v>
       </c>
       <c r="D452" t="s">
-        <v>796</v>
+        <v>987</v>
       </c>
       <c r="E452" t="s">
-        <v>905</v>
+        <v>918</v>
       </c>
       <c r="F452">
         <v>1</v>
@@ -16531,7 +16480,7 @@
         <v>0</v>
       </c>
       <c r="I452">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="453" spans="1:9" x14ac:dyDescent="0.25">
@@ -16539,16 +16488,16 @@
         <v>452</v>
       </c>
       <c r="B453" t="s">
-        <v>906</v>
+        <v>919</v>
       </c>
       <c r="C453" t="s">
         <v>512</v>
       </c>
       <c r="D453" t="s">
-        <v>1004</v>
+        <v>987</v>
       </c>
       <c r="E453" t="s">
-        <v>907</v>
+        <v>920</v>
       </c>
       <c r="F453">
         <v>1</v>
@@ -16568,16 +16517,16 @@
         <v>453</v>
       </c>
       <c r="B454" t="s">
-        <v>908</v>
+        <v>921</v>
       </c>
       <c r="C454" t="s">
         <v>512</v>
       </c>
       <c r="D454" t="s">
-        <v>1004</v>
+        <v>987</v>
       </c>
       <c r="E454" t="s">
-        <v>909</v>
+        <v>922</v>
       </c>
       <c r="F454">
         <v>1</v>
@@ -16597,16 +16546,16 @@
         <v>454</v>
       </c>
       <c r="B455" t="s">
-        <v>910</v>
+        <v>923</v>
       </c>
       <c r="C455" t="s">
         <v>512</v>
       </c>
       <c r="D455" t="s">
-        <v>1004</v>
+        <v>987</v>
       </c>
       <c r="E455" t="s">
-        <v>911</v>
+        <v>924</v>
       </c>
       <c r="F455">
         <v>1</v>
@@ -16626,16 +16575,16 @@
         <v>455</v>
       </c>
       <c r="B456" t="s">
-        <v>912</v>
+        <v>925</v>
       </c>
       <c r="C456" t="s">
         <v>512</v>
       </c>
       <c r="D456" t="s">
-        <v>1004</v>
+        <v>987</v>
       </c>
       <c r="E456" t="s">
-        <v>913</v>
+        <v>926</v>
       </c>
       <c r="F456">
         <v>1</v>
@@ -16655,16 +16604,16 @@
         <v>456</v>
       </c>
       <c r="B457" t="s">
-        <v>914</v>
+        <v>927</v>
       </c>
       <c r="C457" t="s">
         <v>512</v>
       </c>
       <c r="D457" t="s">
-        <v>1004</v>
+        <v>987</v>
       </c>
       <c r="E457" t="s">
-        <v>915</v>
+        <v>928</v>
       </c>
       <c r="F457">
         <v>1</v>
@@ -16684,16 +16633,16 @@
         <v>457</v>
       </c>
       <c r="B458" t="s">
-        <v>916</v>
+        <v>929</v>
       </c>
       <c r="C458" t="s">
         <v>512</v>
       </c>
       <c r="D458" t="s">
-        <v>1004</v>
+        <v>987</v>
       </c>
       <c r="E458" t="s">
-        <v>917</v>
+        <v>930</v>
       </c>
       <c r="F458">
         <v>1</v>
@@ -16713,16 +16662,16 @@
         <v>458</v>
       </c>
       <c r="B459" t="s">
-        <v>918</v>
+        <v>931</v>
       </c>
       <c r="C459" t="s">
         <v>512</v>
       </c>
       <c r="D459" t="s">
-        <v>1004</v>
+        <v>987</v>
       </c>
       <c r="E459" t="s">
-        <v>919</v>
+        <v>932</v>
       </c>
       <c r="F459">
         <v>1</v>
@@ -16742,16 +16691,16 @@
         <v>459</v>
       </c>
       <c r="B460" t="s">
-        <v>920</v>
+        <v>933</v>
       </c>
       <c r="C460" t="s">
         <v>512</v>
       </c>
       <c r="D460" t="s">
-        <v>1004</v>
+        <v>987</v>
       </c>
       <c r="E460" t="s">
-        <v>921</v>
+        <v>934</v>
       </c>
       <c r="F460">
         <v>1</v>
@@ -16771,16 +16720,16 @@
         <v>460</v>
       </c>
       <c r="B461" t="s">
-        <v>922</v>
+        <v>935</v>
       </c>
       <c r="C461" t="s">
         <v>512</v>
       </c>
       <c r="D461" t="s">
-        <v>1004</v>
+        <v>987</v>
       </c>
       <c r="E461" t="s">
-        <v>923</v>
+        <v>936</v>
       </c>
       <c r="F461">
         <v>1</v>
@@ -16800,16 +16749,16 @@
         <v>461</v>
       </c>
       <c r="B462" t="s">
-        <v>924</v>
+        <v>937</v>
       </c>
       <c r="C462" t="s">
         <v>512</v>
       </c>
       <c r="D462" t="s">
-        <v>1004</v>
+        <v>987</v>
       </c>
       <c r="E462" t="s">
-        <v>925</v>
+        <v>938</v>
       </c>
       <c r="F462">
         <v>1</v>
@@ -16829,16 +16778,16 @@
         <v>462</v>
       </c>
       <c r="B463" t="s">
-        <v>926</v>
+        <v>939</v>
       </c>
       <c r="C463" t="s">
         <v>512</v>
       </c>
       <c r="D463" t="s">
-        <v>1004</v>
+        <v>987</v>
       </c>
       <c r="E463" t="s">
-        <v>927</v>
+        <v>940</v>
       </c>
       <c r="F463">
         <v>1</v>
@@ -16858,16 +16807,16 @@
         <v>463</v>
       </c>
       <c r="B464" t="s">
-        <v>928</v>
+        <v>941</v>
       </c>
       <c r="C464" t="s">
         <v>512</v>
       </c>
       <c r="D464" t="s">
-        <v>1004</v>
+        <v>987</v>
       </c>
       <c r="E464" t="s">
-        <v>929</v>
+        <v>942</v>
       </c>
       <c r="F464">
         <v>1</v>
@@ -16887,16 +16836,16 @@
         <v>464</v>
       </c>
       <c r="B465" t="s">
-        <v>930</v>
+        <v>943</v>
       </c>
       <c r="C465" t="s">
         <v>512</v>
       </c>
       <c r="D465" t="s">
-        <v>1004</v>
+        <v>987</v>
       </c>
       <c r="E465" t="s">
-        <v>931</v>
+        <v>944</v>
       </c>
       <c r="F465">
         <v>1</v>
@@ -16916,16 +16865,16 @@
         <v>465</v>
       </c>
       <c r="B466" t="s">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="C466" t="s">
         <v>512</v>
       </c>
       <c r="D466" t="s">
-        <v>1004</v>
+        <v>987</v>
       </c>
       <c r="E466" t="s">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="F466">
         <v>1</v>
@@ -16945,16 +16894,16 @@
         <v>466</v>
       </c>
       <c r="B467" t="s">
-        <v>934</v>
+        <v>947</v>
       </c>
       <c r="C467" t="s">
         <v>512</v>
       </c>
       <c r="D467" t="s">
-        <v>1004</v>
+        <v>987</v>
       </c>
       <c r="E467" t="s">
-        <v>935</v>
+        <v>948</v>
       </c>
       <c r="F467">
         <v>1</v>
@@ -16974,16 +16923,16 @@
         <v>467</v>
       </c>
       <c r="B468" t="s">
-        <v>936</v>
+        <v>949</v>
       </c>
       <c r="C468" t="s">
         <v>512</v>
       </c>
       <c r="D468" t="s">
-        <v>1004</v>
+        <v>987</v>
       </c>
       <c r="E468" t="s">
-        <v>937</v>
+        <v>950</v>
       </c>
       <c r="F468">
         <v>1</v>
@@ -17003,16 +16952,16 @@
         <v>468</v>
       </c>
       <c r="B469" t="s">
-        <v>938</v>
+        <v>951</v>
       </c>
       <c r="C469" t="s">
         <v>512</v>
       </c>
       <c r="D469" t="s">
-        <v>1004</v>
+        <v>987</v>
       </c>
       <c r="E469" t="s">
-        <v>939</v>
+        <v>952</v>
       </c>
       <c r="F469">
         <v>1</v>
@@ -17032,16 +16981,16 @@
         <v>469</v>
       </c>
       <c r="B470" t="s">
-        <v>940</v>
+        <v>953</v>
       </c>
       <c r="C470" t="s">
         <v>512</v>
       </c>
       <c r="D470" t="s">
-        <v>1004</v>
+        <v>987</v>
       </c>
       <c r="E470" t="s">
-        <v>941</v>
+        <v>954</v>
       </c>
       <c r="F470">
         <v>1</v>
@@ -17061,16 +17010,16 @@
         <v>470</v>
       </c>
       <c r="B471" t="s">
-        <v>942</v>
+        <v>955</v>
       </c>
       <c r="C471" t="s">
         <v>512</v>
       </c>
       <c r="D471" t="s">
-        <v>1004</v>
+        <v>987</v>
       </c>
       <c r="E471" t="s">
-        <v>943</v>
+        <v>956</v>
       </c>
       <c r="F471">
         <v>1</v>
@@ -17090,16 +17039,16 @@
         <v>471</v>
       </c>
       <c r="B472" t="s">
-        <v>944</v>
+        <v>957</v>
       </c>
       <c r="C472" t="s">
         <v>512</v>
       </c>
       <c r="D472" t="s">
-        <v>1004</v>
+        <v>987</v>
       </c>
       <c r="E472" t="s">
-        <v>945</v>
+        <v>958</v>
       </c>
       <c r="F472">
         <v>1</v>
@@ -17119,16 +17068,16 @@
         <v>472</v>
       </c>
       <c r="B473" t="s">
-        <v>946</v>
+        <v>959</v>
       </c>
       <c r="C473" t="s">
         <v>512</v>
       </c>
       <c r="D473" t="s">
-        <v>1004</v>
+        <v>987</v>
       </c>
       <c r="E473" t="s">
-        <v>947</v>
+        <v>960</v>
       </c>
       <c r="F473">
         <v>1</v>
@@ -17148,16 +17097,16 @@
         <v>473</v>
       </c>
       <c r="B474" t="s">
-        <v>948</v>
+        <v>961</v>
       </c>
       <c r="C474" t="s">
         <v>512</v>
       </c>
       <c r="D474" t="s">
-        <v>1004</v>
+        <v>987</v>
       </c>
       <c r="E474" t="s">
-        <v>949</v>
+        <v>962</v>
       </c>
       <c r="F474">
         <v>1</v>
@@ -17177,16 +17126,16 @@
         <v>474</v>
       </c>
       <c r="B475" t="s">
-        <v>950</v>
+        <v>963</v>
       </c>
       <c r="C475" t="s">
         <v>512</v>
       </c>
       <c r="D475" t="s">
-        <v>1004</v>
+        <v>987</v>
       </c>
       <c r="E475" t="s">
-        <v>951</v>
+        <v>964</v>
       </c>
       <c r="F475">
         <v>1</v>
@@ -17206,16 +17155,16 @@
         <v>475</v>
       </c>
       <c r="B476" t="s">
-        <v>952</v>
+        <v>965</v>
       </c>
       <c r="C476" t="s">
         <v>512</v>
       </c>
       <c r="D476" t="s">
-        <v>1004</v>
+        <v>987</v>
       </c>
       <c r="E476" t="s">
-        <v>953</v>
+        <v>966</v>
       </c>
       <c r="F476">
         <v>1</v>
@@ -17235,16 +17184,16 @@
         <v>476</v>
       </c>
       <c r="B477" t="s">
-        <v>954</v>
+        <v>967</v>
       </c>
       <c r="C477" t="s">
         <v>512</v>
       </c>
       <c r="D477" t="s">
-        <v>1004</v>
+        <v>987</v>
       </c>
       <c r="E477" t="s">
-        <v>955</v>
+        <v>968</v>
       </c>
       <c r="F477">
         <v>1</v>
@@ -17264,16 +17213,16 @@
         <v>477</v>
       </c>
       <c r="B478" t="s">
-        <v>956</v>
+        <v>969</v>
       </c>
       <c r="C478" t="s">
         <v>512</v>
       </c>
       <c r="D478" t="s">
-        <v>1004</v>
+        <v>987</v>
       </c>
       <c r="E478" t="s">
-        <v>957</v>
+        <v>970</v>
       </c>
       <c r="F478">
         <v>1</v>
@@ -17293,16 +17242,16 @@
         <v>478</v>
       </c>
       <c r="B479" t="s">
-        <v>958</v>
+        <v>971</v>
       </c>
       <c r="C479" t="s">
         <v>512</v>
       </c>
       <c r="D479" t="s">
-        <v>1004</v>
+        <v>987</v>
       </c>
       <c r="E479" t="s">
-        <v>959</v>
+        <v>972</v>
       </c>
       <c r="F479">
         <v>1</v>
@@ -17322,16 +17271,16 @@
         <v>479</v>
       </c>
       <c r="B480" t="s">
-        <v>960</v>
+        <v>973</v>
       </c>
       <c r="C480" t="s">
         <v>512</v>
       </c>
       <c r="D480" t="s">
-        <v>1004</v>
+        <v>987</v>
       </c>
       <c r="E480" t="s">
-        <v>961</v>
+        <v>974</v>
       </c>
       <c r="F480">
         <v>1</v>
@@ -17351,16 +17300,16 @@
         <v>480</v>
       </c>
       <c r="B481" t="s">
-        <v>962</v>
+        <v>975</v>
       </c>
       <c r="C481" t="s">
         <v>512</v>
       </c>
       <c r="D481" t="s">
-        <v>1004</v>
+        <v>987</v>
       </c>
       <c r="E481" t="s">
-        <v>963</v>
+        <v>976</v>
       </c>
       <c r="F481">
         <v>1</v>
@@ -17380,16 +17329,16 @@
         <v>481</v>
       </c>
       <c r="B482" t="s">
-        <v>964</v>
+        <v>977</v>
       </c>
       <c r="C482" t="s">
         <v>512</v>
       </c>
       <c r="D482" t="s">
-        <v>1004</v>
+        <v>987</v>
       </c>
       <c r="E482" t="s">
-        <v>965</v>
+        <v>978</v>
       </c>
       <c r="F482">
         <v>1</v>
@@ -17409,16 +17358,16 @@
         <v>482</v>
       </c>
       <c r="B483" t="s">
-        <v>966</v>
+        <v>979</v>
       </c>
       <c r="C483" t="s">
         <v>512</v>
       </c>
       <c r="D483" t="s">
-        <v>1004</v>
+        <v>987</v>
       </c>
       <c r="E483" t="s">
-        <v>967</v>
+        <v>980</v>
       </c>
       <c r="F483">
         <v>1</v>
@@ -17438,16 +17387,16 @@
         <v>483</v>
       </c>
       <c r="B484" t="s">
-        <v>968</v>
+        <v>981</v>
       </c>
       <c r="C484" t="s">
         <v>512</v>
       </c>
       <c r="D484" t="s">
-        <v>1004</v>
+        <v>987</v>
       </c>
       <c r="E484" t="s">
-        <v>969</v>
+        <v>982</v>
       </c>
       <c r="F484">
         <v>1</v>
@@ -17467,16 +17416,16 @@
         <v>484</v>
       </c>
       <c r="B485" t="s">
-        <v>970</v>
+        <v>983</v>
       </c>
       <c r="C485" t="s">
         <v>512</v>
       </c>
       <c r="D485" t="s">
-        <v>1004</v>
+        <v>987</v>
       </c>
       <c r="E485" t="s">
-        <v>971</v>
+        <v>984</v>
       </c>
       <c r="F485">
         <v>1</v>
@@ -17496,16 +17445,16 @@
         <v>485</v>
       </c>
       <c r="B486" t="s">
-        <v>972</v>
+        <v>985</v>
       </c>
       <c r="C486" t="s">
         <v>512</v>
       </c>
       <c r="D486" t="s">
-        <v>1004</v>
+        <v>987</v>
       </c>
       <c r="E486" t="s">
-        <v>973</v>
+        <v>986</v>
       </c>
       <c r="F486">
         <v>1</v>
@@ -17520,444 +17469,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="487" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A487">
-        <v>486</v>
-      </c>
-      <c r="B487" t="s">
-        <v>974</v>
-      </c>
-      <c r="C487" t="s">
-        <v>512</v>
-      </c>
-      <c r="D487" t="s">
-        <v>1004</v>
-      </c>
-      <c r="E487" t="s">
-        <v>975</v>
-      </c>
-      <c r="F487">
-        <v>1</v>
-      </c>
-      <c r="G487">
-        <v>0</v>
-      </c>
-      <c r="H487">
-        <v>0</v>
-      </c>
-      <c r="I487">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="488" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A488">
-        <v>487</v>
-      </c>
-      <c r="B488" t="s">
-        <v>976</v>
-      </c>
-      <c r="C488" t="s">
-        <v>512</v>
-      </c>
-      <c r="D488" t="s">
-        <v>1004</v>
-      </c>
-      <c r="E488" t="s">
-        <v>977</v>
-      </c>
-      <c r="F488">
-        <v>1</v>
-      </c>
-      <c r="G488">
-        <v>0</v>
-      </c>
-      <c r="H488">
-        <v>0</v>
-      </c>
-      <c r="I488">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="489" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A489">
-        <v>488</v>
-      </c>
-      <c r="B489" t="s">
-        <v>978</v>
-      </c>
-      <c r="C489" t="s">
-        <v>512</v>
-      </c>
-      <c r="D489" t="s">
-        <v>1004</v>
-      </c>
-      <c r="E489" t="s">
-        <v>979</v>
-      </c>
-      <c r="F489">
-        <v>1</v>
-      </c>
-      <c r="G489">
-        <v>0</v>
-      </c>
-      <c r="H489">
-        <v>0</v>
-      </c>
-      <c r="I489">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="490" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A490">
-        <v>489</v>
-      </c>
-      <c r="B490" t="s">
-        <v>980</v>
-      </c>
-      <c r="C490" t="s">
-        <v>512</v>
-      </c>
-      <c r="D490" t="s">
-        <v>1004</v>
-      </c>
-      <c r="E490" t="s">
-        <v>981</v>
-      </c>
-      <c r="F490">
-        <v>1</v>
-      </c>
-      <c r="G490">
-        <v>0</v>
-      </c>
-      <c r="H490">
-        <v>0</v>
-      </c>
-      <c r="I490">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="491" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A491">
-        <v>490</v>
-      </c>
-      <c r="B491" t="s">
-        <v>982</v>
-      </c>
-      <c r="C491" t="s">
-        <v>512</v>
-      </c>
-      <c r="D491" t="s">
-        <v>1004</v>
-      </c>
-      <c r="E491" t="s">
-        <v>983</v>
-      </c>
-      <c r="F491">
-        <v>1</v>
-      </c>
-      <c r="G491">
-        <v>0</v>
-      </c>
-      <c r="H491">
-        <v>0</v>
-      </c>
-      <c r="I491">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="492" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A492">
-        <v>491</v>
-      </c>
-      <c r="B492" t="s">
-        <v>984</v>
-      </c>
-      <c r="C492" t="s">
-        <v>512</v>
-      </c>
-      <c r="D492" t="s">
-        <v>1004</v>
-      </c>
-      <c r="E492" t="s">
-        <v>985</v>
-      </c>
-      <c r="F492">
-        <v>1</v>
-      </c>
-      <c r="G492">
-        <v>0</v>
-      </c>
-      <c r="H492">
-        <v>0</v>
-      </c>
-      <c r="I492">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="493" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A493">
-        <v>492</v>
-      </c>
-      <c r="B493" t="s">
-        <v>986</v>
-      </c>
-      <c r="C493" t="s">
-        <v>512</v>
-      </c>
-      <c r="D493" t="s">
-        <v>1004</v>
-      </c>
-      <c r="E493" t="s">
-        <v>987</v>
-      </c>
-      <c r="F493">
-        <v>1</v>
-      </c>
-      <c r="G493">
-        <v>0</v>
-      </c>
-      <c r="H493">
-        <v>0</v>
-      </c>
-      <c r="I493">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="494" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A494">
-        <v>493</v>
-      </c>
-      <c r="B494" t="s">
-        <v>988</v>
-      </c>
-      <c r="C494" t="s">
-        <v>512</v>
-      </c>
-      <c r="D494" t="s">
-        <v>1004</v>
-      </c>
-      <c r="E494" t="s">
-        <v>989</v>
-      </c>
-      <c r="F494">
-        <v>1</v>
-      </c>
-      <c r="G494">
-        <v>0</v>
-      </c>
-      <c r="H494">
-        <v>0</v>
-      </c>
-      <c r="I494">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="495" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A495">
-        <v>494</v>
-      </c>
-      <c r="B495" t="s">
-        <v>990</v>
-      </c>
-      <c r="C495" t="s">
-        <v>512</v>
-      </c>
-      <c r="D495" t="s">
-        <v>1004</v>
-      </c>
-      <c r="E495" t="s">
-        <v>991</v>
-      </c>
-      <c r="F495">
-        <v>1</v>
-      </c>
-      <c r="G495">
-        <v>0</v>
-      </c>
-      <c r="H495">
-        <v>0</v>
-      </c>
-      <c r="I495">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="496" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A496">
-        <v>495</v>
-      </c>
-      <c r="B496" t="s">
-        <v>992</v>
-      </c>
-      <c r="C496" t="s">
-        <v>512</v>
-      </c>
-      <c r="D496" t="s">
-        <v>1004</v>
-      </c>
-      <c r="E496" t="s">
-        <v>993</v>
-      </c>
-      <c r="F496">
-        <v>1</v>
-      </c>
-      <c r="G496">
-        <v>0</v>
-      </c>
-      <c r="H496">
-        <v>0</v>
-      </c>
-      <c r="I496">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="497" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A497">
-        <v>496</v>
-      </c>
-      <c r="B497" t="s">
-        <v>994</v>
-      </c>
-      <c r="C497" t="s">
-        <v>512</v>
-      </c>
-      <c r="D497" t="s">
-        <v>1004</v>
-      </c>
-      <c r="E497" t="s">
-        <v>995</v>
-      </c>
-      <c r="F497">
-        <v>1</v>
-      </c>
-      <c r="G497">
-        <v>0</v>
-      </c>
-      <c r="H497">
-        <v>0</v>
-      </c>
-      <c r="I497">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="498" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A498">
-        <v>497</v>
-      </c>
-      <c r="B498" t="s">
-        <v>996</v>
-      </c>
-      <c r="C498" t="s">
-        <v>512</v>
-      </c>
-      <c r="D498" t="s">
-        <v>1004</v>
-      </c>
-      <c r="E498" t="s">
-        <v>997</v>
-      </c>
-      <c r="F498">
-        <v>1</v>
-      </c>
-      <c r="G498">
-        <v>0</v>
-      </c>
-      <c r="H498">
-        <v>0</v>
-      </c>
-      <c r="I498">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="499" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A499">
-        <v>498</v>
-      </c>
-      <c r="B499" t="s">
-        <v>998</v>
-      </c>
-      <c r="C499" t="s">
-        <v>512</v>
-      </c>
-      <c r="D499" t="s">
-        <v>1004</v>
-      </c>
-      <c r="E499" t="s">
-        <v>999</v>
-      </c>
-      <c r="F499">
-        <v>1</v>
-      </c>
-      <c r="G499">
-        <v>0</v>
-      </c>
-      <c r="H499">
-        <v>0</v>
-      </c>
-      <c r="I499">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="500" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A500">
-        <v>499</v>
-      </c>
-      <c r="B500" t="s">
-        <v>1000</v>
-      </c>
-      <c r="C500" t="s">
-        <v>512</v>
-      </c>
-      <c r="D500" t="s">
-        <v>1004</v>
-      </c>
-      <c r="E500" t="s">
-        <v>1001</v>
-      </c>
-      <c r="F500">
-        <v>1</v>
-      </c>
-      <c r="G500">
-        <v>0</v>
-      </c>
-      <c r="H500">
-        <v>0</v>
-      </c>
-      <c r="I500">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="501" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A501">
-        <v>500</v>
-      </c>
-      <c r="B501" t="s">
-        <v>1002</v>
-      </c>
-      <c r="C501" t="s">
-        <v>512</v>
-      </c>
-      <c r="D501" t="s">
-        <v>1004</v>
-      </c>
-      <c r="E501" t="s">
-        <v>1003</v>
-      </c>
-      <c r="F501">
-        <v>1</v>
-      </c>
-      <c r="G501">
-        <v>0</v>
-      </c>
-      <c r="H501">
-        <v>0</v>
-      </c>
-      <c r="I501">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I906">
-    <sortCondition ref="A1:A906"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I891">
+    <sortCondition ref="A1:A891"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
